--- a/artfynd/A 32579-2025 artfynd.xlsx
+++ b/artfynd/A 32579-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>126670785</v>
       </c>
       <c r="B5" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126670920</v>
       </c>
       <c r="B6" t="n">
-        <v>103803</v>
+        <v>103878</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126672263</v>
       </c>
       <c r="B7" t="n">
-        <v>103803</v>
+        <v>103878</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126671762</v>
       </c>
       <c r="B8" t="n">
-        <v>103803</v>
+        <v>103878</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>126674486</v>
       </c>
       <c r="B10" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 32579-2025 artfynd.xlsx
+++ b/artfynd/A 32579-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>126670785</v>
       </c>
       <c r="B5" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126670920</v>
       </c>
       <c r="B6" t="n">
-        <v>103878</v>
+        <v>103884</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126672263</v>
       </c>
       <c r="B7" t="n">
-        <v>103878</v>
+        <v>103884</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126671762</v>
       </c>
       <c r="B8" t="n">
-        <v>103878</v>
+        <v>103884</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>126674486</v>
       </c>
       <c r="B10" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 32579-2025 artfynd.xlsx
+++ b/artfynd/A 32579-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>126670785</v>
       </c>
       <c r="B5" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126670920</v>
       </c>
       <c r="B6" t="n">
-        <v>103884</v>
+        <v>103885</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126672263</v>
       </c>
       <c r="B7" t="n">
-        <v>103884</v>
+        <v>103885</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126671762</v>
       </c>
       <c r="B8" t="n">
-        <v>103884</v>
+        <v>103885</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32579-2025 artfynd.xlsx
+++ b/artfynd/A 32579-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>126670785</v>
       </c>
       <c r="B5" t="n">
-        <v>98464</v>
+        <v>98457</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126670920</v>
       </c>
       <c r="B6" t="n">
-        <v>103885</v>
+        <v>103878</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126672263</v>
       </c>
       <c r="B7" t="n">
-        <v>103885</v>
+        <v>103878</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126671762</v>
       </c>
       <c r="B8" t="n">
-        <v>103885</v>
+        <v>103878</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>126674486</v>
       </c>
       <c r="B10" t="n">
-        <v>80117</v>
+        <v>80114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
